--- a/output/pdf_financials_xlsx/GPM.xlsx
+++ b/output/pdf_financials_xlsx/GPM.xlsx
@@ -5721,46 +5721,46 @@
         <v>2.525674</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.59853</v>
+        <v>3.538936</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.868987</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.303987</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.563401</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.563401</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.996495</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.518549</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.230528</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.485274</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>15.947919</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>16.345647</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>17.400093</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>17.585906</v>
       </c>
     </row>
     <row r="93">
@@ -7503,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
@@ -9522,7 +9522,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -9616,7 +9620,11 @@
           <t>Warrant reserve (note 12)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10466,7 +10474,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10560,7 +10572,11 @@
           <t>Warrant reserve (note 12)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11284,7 +11300,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11378,7 +11398,11 @@
           <t>Warrant reserve (note 11)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12518,7 +12542,11 @@
           <t>Warrant reserve (note 11)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -13292,7 +13320,11 @@
           <t>Warrant reserve (note 10)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13770,7 +13802,11 @@
           <t>Warrant reserve (note 9)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14716,7 +14752,11 @@
           <t>Warrant reserve (note 12)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -15180,7 +15220,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -16254,7 +16298,11 @@
           <t>Warrant reserve 2,868,987</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -18630,7 +18678,11 @@
           <t>Shares to be issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GPM.xlsx
+++ b/output/pdf_financials_xlsx/GPM.xlsx
@@ -1005,46 +1005,46 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.024594</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.043184</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.023126</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.021724</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.020442</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.010575</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.010154</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00624</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.006081</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004452</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003982</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.014461</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.02842</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.054216</v>
       </c>
     </row>
     <row r="13">
@@ -1976,46 +1976,46 @@
         <v>-0.829361</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.173486</v>
+        <v>-0.19808</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.894607</v>
+        <v>-4.937791</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.002738</v>
+        <v>-2.025864</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.232991</v>
+        <v>-1.254715</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.910955</v>
+        <v>-2.931397</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.331539</v>
+        <v>-1.342114</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.378406</v>
+        <v>-0.38856</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.154272</v>
+        <v>-2.160512</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.754957</v>
+        <v>-0.761038</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.6591</v>
+        <v>-0.663552</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.329814</v>
+        <v>-0.333796</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.688382</v>
+        <v>-0.702843</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.959769</v>
+        <v>-0.988189</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.925882</v>
+        <v>-2.980098</v>
       </c>
     </row>
     <row r="28">
@@ -2086,46 +2086,46 @@
         <v>-0.829361</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.173486</v>
+        <v>-0.19808</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.894607</v>
+        <v>-4.937791</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.002738</v>
+        <v>-2.025864</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.232991</v>
+        <v>-1.254715</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.910955</v>
+        <v>-2.931397</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.331539</v>
+        <v>-1.342114</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.378406</v>
+        <v>-0.38856</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.154272</v>
+        <v>-2.160512</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.754957</v>
+        <v>-0.761038</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.6591</v>
+        <v>-0.663552</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.329814</v>
+        <v>-0.333796</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.688382</v>
+        <v>-0.702843</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.959769</v>
+        <v>-0.988189</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.925882</v>
+        <v>-2.980098</v>
       </c>
     </row>
     <row r="30">
@@ -2380,43 +2380,43 @@
         <v>2.872044</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>9.550084</v>
+        <v>5.402508</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.68491</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.658065</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.299287</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.000998</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.827393</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.231889</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.399674</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.312374</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.227136</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.221738</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.876908</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.522572</v>
       </c>
     </row>
     <row r="35">
@@ -2490,43 +2490,43 @@
         <v>3.032044</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>9.755374</v>
+        <v>5.607798</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0575</v>
+        <v>4.74241</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.04</v>
+        <v>4.698065</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.025</v>
+        <v>2.324287</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.0175</v>
+        <v>1.018498</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.025</v>
+        <v>1.852393</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.021853</v>
+        <v>0.253742</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.013503</v>
+        <v>0.413177</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.019509</v>
+        <v>0.331883</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.9e-05</v>
+        <v>0.227165</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>3.1e-05</v>
+        <v>0.221769</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>8.1e-05</v>
+        <v>0.876989</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.000268</v>
+        <v>2.52284</v>
       </c>
     </row>
     <row r="37">
@@ -3150,31 +3150,31 @@
         <v>0.010457</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.054531</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.733574</v>
+        <v>0.048664</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.715498</v>
+        <v>0.057433</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.403912</v>
+        <v>0.104625</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.52279</v>
+        <v>0.521792</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.938216</v>
+        <v>0.110823</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.298078</v>
+        <v>0.066189</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.435745</v>
+        <v>0.036071</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.347942</v>
+        <v>0.035568</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -25196,7 +25196,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -26062,7 +26062,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">

--- a/output/pdf_financials_xlsx/GPM.xlsx
+++ b/output/pdf_financials_xlsx/GPM.xlsx
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.326048</v>
+        <v>-0.326048</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.78749</v>
+        <v>-0.78749</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-1e-06</v>
@@ -2548,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.000679</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.001771</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.00161</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
@@ -2737,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.031028</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.000808</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.000679</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.001771</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.00161</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0</v>
@@ -2792,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.031028</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.000808</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0</v>
@@ -3153,13 +3153,13 @@
         <v>0.054531</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.048664</v>
+        <v>0.047985</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.057433</v>
+        <v>0.055662</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.104625</v>
+        <v>0.103015</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.521792</v>
@@ -6244,13 +6244,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.031636</v>
+        <v>-0.111281</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.003857</v>
+        <v>0.261104</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.010876</v>
+        <v>0.010457</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -22710,7 +22710,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="n">
         <v>-0.326048</v>
       </c>
@@ -22900,7 +22904,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -24422,7 +24430,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="n">
         <v>-0.142917</v>
       </c>
@@ -32744,7 +32756,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>0.326048</v>
       </c>
